--- a/capstone-project/public/Private_Template.xlsx
+++ b/capstone-project/public/Private_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lheriza Miranda\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FFE6D36-3D83-4703-9326-1A5CF1D43AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA18BF0-1E7F-4781-8056-3E727758BB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F5BB2B95-6DA3-4F50-AA78-4FECCFEAE9D8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5BB2B95-6DA3-4F50-AA78-4FECCFEAE9D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,13 +74,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0627A2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -110,20 +124,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -132,6 +147,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0627A2"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -147,16 +167,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1192531</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>651510</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>78105</xdr:rowOff>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1828801</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1318259</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>172143</xdr:rowOff>
+      <xdr:rowOff>156444</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -186,8 +206,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1802131" y="78105"/>
-          <a:ext cx="636270" cy="804603"/>
+          <a:off x="7639050" y="22860"/>
+          <a:ext cx="666749" cy="865104"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -202,6 +222,50 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1325880</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1949020</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{116513E6-6058-4B32-AC61-DCD169BB8969}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1935480" y="167640"/>
+          <a:ext cx="623140" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -526,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DEE60F8-3751-4ED6-81FE-A14FECBD5354}">
-  <dimension ref="B2:G7"/>
+  <dimension ref="B3:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.44140625" customWidth="1"/>
@@ -534,52 +598,46 @@
     <col min="4" max="4" width="15.5546875" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="28.44140625" customWidth="1"/>
+    <col min="7" max="7" width="45.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="1"/>
-    </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-    </row>
-    <row r="6" spans="2:7" s="2" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="2:7" s="1" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
